--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -647,7 +647,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 09:59</t>
+          <t>Son Güncelleme: 2026-06-05 10:22</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -1261,7 +1261,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 09:59</t>
+          <t>Son Güncelleme: 2026-06-05 10:22</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -2229,7 +2229,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 09:59</t>
+          <t>Son Güncelleme: 2026-06-05 10:22</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3061,7 +3061,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 09:59</t>
+          <t>Son Güncelleme: 2026-06-05 10:22</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3180,7 +3180,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 09:59</t>
+          <t>Son Güncelleme: 2026-06-05 10:22</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3431,7 +3431,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 09:59</t>
+          <t>Son Güncelleme: 2026-06-05 10:22</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3556,7 +3556,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 09:59</t>
+          <t>Son Güncelleme: 2026-06-05 10:22</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H4" s="30" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H5" s="30" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>0</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H8" s="30" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H9" s="30" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H10" s="30" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H11" s="30" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>870000</v>
+        <v>940000</v>
       </c>
       <c r="H12" s="30" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -41,9 +41,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
@@ -60,6 +57,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -105,19 +105,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -137,96 +131,93 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,595 +602,595 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BIST RankingBot Yatırımcı Raporu</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Piyasa Rejimi: Risk ON</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Aktif Model: volume_heavy</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı: 64.35/100</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>BU AY YAPILACAKLAR</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>AL: SISE.IS, FROTO.IS, BIMAS.IS, TOASO.IS, ARCLK.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>AZALT: ASELS.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ÇIK: EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NAKIT: %50</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Neden Nakit Tutuluyor?</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>- Yeterli sayıda yüksek kaliteli fırsat bulunamadı.</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>- Opportunity filter aktif.</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Tablo çekiciliğe göre sıralıdır; yüksek conviction daha güçlü adayları gösterir.</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Qualified opportunities count: 5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Allocation TL</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Expected Return %</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Expected Return TL</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Stop Price</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Risk/Reward</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Conviction</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Rejected opportunities count: 5</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.1243871586137416</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>12438.71586137416</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="7" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>713.1262528103351</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="8" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="8" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Cash allocation %: %50</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="7" t="n">
         <v>0.1065382972466226</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>10653.82972466226</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>1209.604218552528</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="8" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="8" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="7" t="n">
         <v>0.09833656824386003</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>9833.656824386002</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="7" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>147.5572851699831</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="8" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="8" t="n">
         <v>352.6875</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>0.3001066394834209</v>
       </c>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="7" t="n">
         <v>0.09391563882388926</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>9391.563882388926</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="7" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>337.7588530847005</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="8" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="8" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="6" t="n">
         <v>0.5672232190119821</v>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="7" t="n">
         <v>0.07682233707188654</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>7682.233707188654</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="7" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>244.7772522795647</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="8" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>0.6372554171334678</v>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="13" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1238,944 +1229,944 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Aylık Yatırımcı Özeti</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Toplam önerilen/satılacak satır: 13</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Renkler: AL yeşil, TUT sarı, SAT kırmızı.</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bu rapor araştırma amaçlıdır; otomatik emir veya yatırım tavsiyesi değildir.</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt %</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta %</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst %</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt Fiyat</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta Fiyat</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst Fiyat</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Stop / Risk Fiyatı</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Ana Sebep</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Risk Notu</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.0420559802578865</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1156036872656343</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="15" t="n">
         <v>38.31776078968454</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="15" t="n">
         <v>39.79358124262377</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="15" t="n">
         <v>44.62414749062538</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="15" t="n">
         <v>37.54126859386067</v>
       </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="15" t="n">
+      <c r="M8" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="15" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="18" t="n">
+      <c r="M9" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="19" t="n">
         <v>-0.0046916890080428</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.1020951406282874</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>369.5082104557641</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>409.1528209582517</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>352.6875</v>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="18" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.06340373236672001</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.07252410609256819</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>317.4671354034002</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="18" t="n">
+      <c r="M11" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>102.5999984741211</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="16" t="n">
         <v>-0.0448028308183779</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>0.0559687682788319</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="15" t="n">
         <v>98.00322810051922</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="15" t="n">
         <v>102.0206973756039</v>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="15" t="n">
         <v>108.3423940141277</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="15" t="n">
         <v>97.46999855041503</v>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="15" t="n">
+      <c r="M12" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N12" s="15" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="15" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>23.05999946594238</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0633746386509592</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.0814151454989152</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="15" t="n">
         <v>21.59858033249697</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="15" t="n">
         <v>22.38352252170423</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="15" t="n">
         <v>24.93743267766699</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="15" t="n">
         <v>21.56527333559732</v>
       </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="15" t="n">
+      <c r="M13" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="21" t="n">
         <v>384</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="22" t="n">
         <v>-0.0281690730134268</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="22" t="n">
         <v>0.08543155919911009</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="21" t="n">
         <v>373.1830759628441</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="21" t="n">
         <v>389.7266192813116</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="21" t="n">
         <v>416.8057187324583</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="21" t="n">
         <v>359.9101054961429</v>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="21" t="n">
+      <c r="M14" s="20" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="19" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="18" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <v>104</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="19" t="n">
         <v>-0.0155083176665838</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.08243455158337749</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="18" t="n">
         <v>102.3871349626753</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>112.5731933646713</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>98.8</v>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="18" t="n">
+      <c r="M16" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="N16" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O16" s="18" t="inlineStr">
+      <c r="O16" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="15" t="n">
         <v>291.5</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="16" t="n">
         <v>-0.0386983355086648</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="16" t="n">
         <v>0.0471518681568155</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="15" t="n">
         <v>280.2194351992242</v>
       </c>
-      <c r="I17" s="16" t="n">
+      <c r="I17" s="15" t="n">
         <v>289.4402953699822</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="15" t="n">
         <v>305.2447695677117</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="15" t="n">
         <v>276.925</v>
       </c>
-      <c r="L17" s="15" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="15" t="n">
+      <c r="M17" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N17" s="15" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O17" s="15" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="24" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.09996593281665379</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0287358367126191</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="24" t="n">
         <v>87.01823150556903</v>
       </c>
-      <c r="J18" s="25" t="n">
+      <c r="J18" s="24" t="n">
         <v>91.55748946742311</v>
       </c>
-      <c r="K18" s="25" t="n">
+      <c r="K18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n">
+      <c r="M18" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N18" s="24" t="inlineStr">
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif</t>
         </is>
       </c>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="24" t="n">
         <v>63.70000076293945</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0615218226622063</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>0.1090908628521543</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="24" t="n">
         <v>59.78106061241949</v>
       </c>
-      <c r="I19" s="25" t="n">
+      <c r="I19" s="24" t="n">
         <v>63.40140776872636</v>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="J19" s="24" t="n">
         <v>70.64908880985141</v>
       </c>
-      <c r="K19" s="25" t="n">
+      <c r="K19" s="24" t="n">
         <v>59.66295737853054</v>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n">
+      <c r="M19" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N19" s="24" t="inlineStr">
+      <c r="N19" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var</t>
         </is>
       </c>
-      <c r="O19" s="24" t="inlineStr">
+      <c r="O19" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="24" t="n">
         <v>33.41999816894531</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="25" t="n">
         <v>-0.0659425781939114</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="25" t="n">
         <v>0.1010665940075984</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="I20" s="25" t="n">
+      <c r="I20" s="24" t="n">
         <v>32.38346565501426</v>
       </c>
-      <c r="J20" s="25" t="n">
+      <c r="J20" s="24" t="n">
         <v>36.79764355562079</v>
       </c>
-      <c r="K20" s="25" t="n">
+      <c r="K20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n">
+      <c r="M20" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="N20" s="23" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O20" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
@@ -2210,824 +2201,824 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1A Momentum</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>3A Momentum</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>6A Momentum</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Hacim Değişimi</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Trend Durumu</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Beklenen Getiri Orta %</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="16" t="n">
         <v>0.1862395774600724</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="16" t="n">
         <v>0.2539185102925374</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="16" t="n">
         <v>0.6764458917342262</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="16" t="n">
         <v>0.041267190077997</v>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="16" t="n">
         <v>0.0307341425767416</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="J5" s="19" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="K5" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.0013486176668915</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.100815418828762</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.3632607485858201</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="19" t="n">
         <v>-0.1103780044876269</v>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="19" t="n">
         <v>0.023589744633299</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="19" t="n">
         <v>-0.0025273799494524</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>-0.0189264227791532</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.3768329115958089</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>-0.1760804208636897</v>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="19" t="n">
         <v>0.0273607577956114</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.08474576386540381</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.1506622857438071</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1173328587488999</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="16" t="n">
         <v>0.0313938948468988</v>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>0.0219305756012054</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="16" t="n">
         <v>-0.07091056609677771</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="16" t="n">
         <v>0.3013544220943314</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <v>0.35647055682014</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="16" t="n">
         <v>-0.4658997689756274</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="16" t="n">
         <v>0.0324095005412434</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>-0.0975323149236192</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="22" t="n">
         <v>0.234726688102894</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="22" t="n">
         <v>1.093784148197624</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="22" t="n">
         <v>-0.3248706883042701</v>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="22" t="n">
         <v>0.0313670501352306</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="19" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="19" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="19" t="n">
         <v>-0.0739091970276476</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <v>-0.1231028554971428</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>-0.0160832260863227</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="19" t="n">
         <v>-0.0886630889314125</v>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="19" t="n">
         <v>0.0203560631794317</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0731319554848967</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0642054574638844</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.068744271310724</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="16" t="n">
         <v>-0.1125189107212077</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="16" t="n">
         <v>0.0231561831887904</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="K13" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="27" t="n">
         <v>-0.0805734197027545</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="27" t="n">
         <v>-0.0596758909696701</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="27" t="n">
         <v>0.1458106229539508</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="27" t="n">
         <v>-0.2599604463071995</v>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="27" t="n">
         <v>0.0209928798538189</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="27" t="n">
         <v>0.0070464703305382</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="27" t="n">
         <v>-0.0723436224182088</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="27" t="n">
         <v>-0.218580848518051</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="27" t="n">
         <v>-0.07793667413424429</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="27" t="n">
         <v>-0.0069595372522321</v>
       </c>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="27" t="n">
         <v>0.0279986421832064</v>
       </c>
-      <c r="K15" s="28" t="n">
+      <c r="K15" s="27" t="n">
         <v>0.0063124281375852</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="27" t="n">
         <v>-0.1110708025535955</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="27" t="n">
         <v>0.1808376609273443</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="27" t="n">
         <v>0.3087414111063782</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="27" t="n">
         <v>-0.4371995375985574</v>
       </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="27" t="n">
         <v>0.0254253869317556</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="27" t="n">
         <v>0.0179805767303264</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="25" t="n">
         <v>-0.0743629892086322</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="25" t="n">
         <v>-0.1387634300955811</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="25" t="n">
         <v>0.1041495071207343</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="25" t="n">
         <v>-0.137952192271936</v>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="25" t="n">
         <v>0.02615590712964</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="25" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="25" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0858862988621121</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.2407996860197412</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>-0.053257821777556</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="25" t="n">
         <v>-0.0414981713743457</v>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="25" t="n">
         <v>0.0305942800876695</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="27" t="n">
         <v>-0.0597432263673228</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="27" t="n">
         <v>-0.167161244124102</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="27" t="n">
         <v>-0.1621890850921175</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="27" t="n">
         <v>-0.2601417240448666</v>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="28" t="n">
+      <c r="J20" s="27" t="n">
         <v>0.0215890519221315</v>
       </c>
-      <c r="K20" s="28" t="n">
+      <c r="K20" s="27" t="n">
         <v>0.0408327384185252</v>
       </c>
     </row>
@@ -3051,100 +3042,100 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisseler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>SISE.IS, BIMAS.IS, TOASO.IS, FROTO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Nakit kuralı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nitelikli fırsat sayısı</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3170,232 +3161,232 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
@@ -3421,94 +3412,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Gösterge</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -3540,342 +3531,342 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Aktif Pozisyon</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Giriş Tarihi</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Gerçekleşmemiş PnL</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Benchmark Getirisi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H4" s="30" t="n">
+      <c r="G4" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H4" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H5" s="30" t="n">
+      <c r="G5" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H5" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H6" s="30" t="n">
+      <c r="G6" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H6" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H7" s="30" t="n">
+      <c r="G7" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H7" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H8" s="30" t="n">
+      <c r="G8" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H8" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H9" s="30" t="n">
+      <c r="G9" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H9" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="28" t="n">
         <v>-3.637978807091713e-12</v>
       </c>
-      <c r="G10" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H10" s="30" t="n">
+      <c r="G10" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H11" s="30" t="n">
+      <c r="G11" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H11" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H12" s="30" t="n">
+      <c r="G12" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H12" s="29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -41,6 +41,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
@@ -57,9 +60,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -105,13 +105,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -131,93 +137,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,595 +611,595 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>BIST RankingBot Yatırımcı Raporu</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Piyasa Rejimi: Risk ON</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Aktif Model: volume_heavy</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Güven Puanı: 64.35/100</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>BU AY YAPILACAKLAR</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>AL: SISE.IS, FROTO.IS, BIMAS.IS, TOASO.IS, ARCLK.IS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>AZALT: ASELS.IS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>ÇIK: EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>NAKIT: %50</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Neden Nakit Tutuluyor?</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>- Yeterli sayıda yüksek kaliteli fırsat bulunamadı.</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>- Opportunity filter aktif.</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tablo çekiciliğe göre sıralıdır; yüksek conviction daha güçlü adayları gösterir.</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Qualified opportunities count: 5</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Allocation TL</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Expected Return %</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Expected Return TL</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Stop Price</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>Risk/Reward</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>Conviction</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Rejected opportunities count: 5</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="8" t="n">
         <v>0.1243871586137416</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="9" t="n">
         <v>12438.71586137416</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="9" t="n">
         <v>713.1262528103351</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="9" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="9" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="7" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Cash allocation %: %50</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="8" t="n">
         <v>0.1065382972466226</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <v>10653.82972466226</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>1209.604218552528</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="9" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K21" s="6" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="8" t="n">
         <v>0.09833656824386003</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="9" t="n">
         <v>9833.656824386002</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="9" t="n">
         <v>147.5572851699831</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="9" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="9" t="n">
         <v>352.6875</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <v>0.3001066394834209</v>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="8" t="n">
         <v>0.09391563882388926</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="9" t="n">
         <v>9391.563882388926</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>337.7588530847005</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="9" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="9" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="7" t="n">
         <v>0.5672232190119821</v>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="8" t="n">
         <v>0.07682233707188654</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="9" t="n">
         <v>7682.233707188654</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="9" t="n">
         <v>244.7772522795647</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="9" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="9" t="n">
         <v>98.8</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="7" t="n">
         <v>0.6372554171334678</v>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1229,944 +1238,944 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Aylık Yatırımcı Özeti</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Toplam önerilen/satılacak satır: 13</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Renkler: AL yeşil, TUT sarı, SAT kırmızı.</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Bu rapor araştırma amaçlıdır; otomatik emir veya yatırım tavsiyesi değildir.</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Hedef Alt %</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Hedef Orta %</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Hedef Üst %</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Hedef Alt Fiyat</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Hedef Orta Fiyat</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Hedef Üst Fiyat</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>Stop / Risk Fiyatı</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>Ana Sebep</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>Risk Notu</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>-0.0420559802578865</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>-0.0051604689344056</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>0.1156036872656343</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="16" t="n">
         <v>38.31776078968454</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="16" t="n">
         <v>39.79358124262377</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="16" t="n">
         <v>44.62414749062538</v>
       </c>
-      <c r="K8" s="15" t="n">
+      <c r="K8" s="16" t="n">
         <v>37.54126859386067</v>
       </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="L8" s="15" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="N8" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="20" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="19" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="19" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="18" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <v>-0.0046916890080428</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>0.1020951406282874</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <v>369.5082104557641</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="19" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>409.1528209582517</v>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="K10" s="19" t="n">
         <v>352.6875</v>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="18" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="18" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>-0.06340373236672001</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>0.07252410609256819</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="19" t="n">
         <v>317.4671354034002</v>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="K11" s="19" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="18" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>102.5999984741211</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>-0.0448028308183779</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>-0.0056462096211761</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>0.0559687682788319</v>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="16" t="n">
         <v>98.00322810051922</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="16" t="n">
         <v>102.0206973756039</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>108.3423940141277</v>
       </c>
-      <c r="K12" s="15" t="n">
+      <c r="K12" s="16" t="n">
         <v>97.46999855041503</v>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="L12" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N12" s="14" t="inlineStr">
+      <c r="N12" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="O12" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>23.05999946594238</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>-0.0633746386509592</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>-0.0293355143063753</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>0.0814151454989152</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="16" t="n">
         <v>21.59858033249697</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="16" t="n">
         <v>22.38352252170423</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="16" t="n">
         <v>24.93743267766699</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="16" t="n">
         <v>21.56527333559732</v>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="14" t="inlineStr">
+      <c r="O13" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>384</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="23" t="n">
         <v>-0.0281690730134268</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>0.0149130710450822</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>0.08543155919911009</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>373.1830759628441</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>389.7266192813116</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>416.8057187324583</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="K14" s="22" t="n">
         <v>359.9101054961429</v>
       </c>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="20" t="n">
+      <c r="M14" s="21" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="20" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O14" s="20" t="inlineStr">
+      <c r="O14" s="21" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="20" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="20" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="19" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="19" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="19" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="K15" s="19" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="17" t="n">
+      <c r="M15" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="18" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O15" s="18" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="n">
+      <c r="A16" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>104</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="20" t="n">
         <v>-0.0155083176665838</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="20" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="20" t="n">
         <v>0.08243455158337749</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="19" t="n">
         <v>102.3871349626753</v>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="19" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="19" t="n">
         <v>112.5731933646713</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="19" t="n">
         <v>98.8</v>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="17" t="n">
+      <c r="M16" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="18" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="O16" s="18" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>291.5</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>-0.0386983355086648</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>-0.0070658820926857</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <v>0.0471518681568155</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="16" t="n">
         <v>280.2194351992242</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="16" t="n">
         <v>289.4402953699822</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="16" t="n">
         <v>305.2447695677117</v>
       </c>
-      <c r="K17" s="15" t="n">
+      <c r="K17" s="16" t="n">
         <v>276.925</v>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="25" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>-0.09996593281665379</v>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>-0.0222670617351794</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="26" t="n">
         <v>0.0287358367126191</v>
       </c>
-      <c r="H18" s="24" t="n">
+      <c r="H18" s="25" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="I18" s="24" t="n">
+      <c r="I18" s="25" t="n">
         <v>87.01823150556903</v>
       </c>
-      <c r="J18" s="24" t="n">
+      <c r="J18" s="25" t="n">
         <v>91.55748946742311</v>
       </c>
-      <c r="K18" s="24" t="n">
+      <c r="K18" s="25" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="L18" s="23" t="inlineStr">
+      <c r="L18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M18" s="23" t="n">
+      <c r="M18" s="24" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N18" s="23" t="inlineStr">
+      <c r="N18" s="24" t="inlineStr">
         <is>
           <t>6A momentum pozitif</t>
         </is>
       </c>
-      <c r="O18" s="23" t="inlineStr">
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <v>63.70000076293945</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>-0.0615218226622063</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <v>-0.004687488079071</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>0.1090908628521543</v>
       </c>
-      <c r="H19" s="24" t="n">
+      <c r="H19" s="25" t="n">
         <v>59.78106061241949</v>
       </c>
-      <c r="I19" s="24" t="n">
+      <c r="I19" s="25" t="n">
         <v>63.40140776872636</v>
       </c>
-      <c r="J19" s="24" t="n">
+      <c r="J19" s="25" t="n">
         <v>70.64908880985141</v>
       </c>
-      <c r="K19" s="24" t="n">
+      <c r="K19" s="25" t="n">
         <v>59.66295737853054</v>
       </c>
-      <c r="L19" s="23" t="inlineStr">
+      <c r="L19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M19" s="23" t="n">
+      <c r="M19" s="24" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N19" s="23" t="inlineStr">
+      <c r="N19" s="24" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var</t>
         </is>
       </c>
-      <c r="O19" s="23" t="inlineStr">
+      <c r="O19" s="24" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="n">
+      <c r="A20" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="25" t="n">
         <v>33.41999816894531</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <v>-0.0659425781939114</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="26" t="n">
         <v>-0.0310153372448183</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="26" t="n">
         <v>0.1010665940075984</v>
       </c>
-      <c r="H20" s="24" t="n">
+      <c r="H20" s="25" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="I20" s="24" t="n">
+      <c r="I20" s="25" t="n">
         <v>32.38346565501426</v>
       </c>
-      <c r="J20" s="24" t="n">
+      <c r="J20" s="25" t="n">
         <v>36.79764355562079</v>
       </c>
-      <c r="K20" s="24" t="n">
+      <c r="K20" s="25" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M20" s="23" t="n">
+      <c r="M20" s="24" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N20" s="23" t="inlineStr">
+      <c r="N20" s="24" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O20" s="23" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
@@ -2201,824 +2210,824 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>1A Momentum</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>3A Momentum</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>6A Momentum</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Hacim Değişimi</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Trend Durumu</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Beklenen Getiri Orta %</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>0.1862395774600724</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>0.2539185102925374</v>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="17" t="n">
         <v>0.6764458917342262</v>
       </c>
-      <c r="H4" s="16" t="n">
+      <c r="H4" s="17" t="n">
         <v>0.041267190077997</v>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
+      <c r="J4" s="17" t="n">
         <v>0.0307341425767416</v>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="17" t="n">
         <v>-0.0051604689344056</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="20" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="20" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="20" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="20" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="20" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="20" t="n">
         <v>0.0013486176668915</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>0.100815418828762</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="20" t="n">
         <v>0.3632607485858201</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="20" t="n">
         <v>-0.1103780044876269</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="20" t="n">
         <v>0.023589744633299</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="20" t="n">
         <v>0.0150053319741709</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>-0.0025273799494524</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>-0.0189264227791532</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="20" t="n">
         <v>0.3768329115958089</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="20" t="n">
         <v>-0.1760804208636897</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="20" t="n">
         <v>0.0273607577956114</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="20" t="n">
         <v>0.035964069170425</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>-0.08474576386540381</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>-0.1506622857438071</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>0.1173328587488999</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <v>0.0313938948468988</v>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="17" t="n">
         <v>0.0219305756012054</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="17" t="n">
         <v>-0.0056462096211761</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>-0.07091056609677771</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>0.3013544220943314</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>0.35647055682014</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <v>-0.4658997689756274</v>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="16" t="n">
+      <c r="J9" s="17" t="n">
         <v>0.0324095005412434</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="17" t="n">
         <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>-0.0975323149236192</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>0.234726688102894</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="23" t="n">
         <v>1.093784148197624</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="23" t="n">
         <v>-0.3248706883042701</v>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="23" t="n">
         <v>0.0313670501352306</v>
       </c>
-      <c r="K10" s="22" t="n">
+      <c r="K10" s="23" t="n">
         <v>0.0149130710450822</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="20" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="20" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="20" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>-0.0739091970276476</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>-0.1231028554971428</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>-0.0160832260863227</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="20" t="n">
         <v>-0.0886630889314125</v>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="20" t="n">
         <v>0.0203560631794317</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="20" t="n">
         <v>0.0318627708566734</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>-0.0731319554848967</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>-0.0642054574638844</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>0.068744271310724</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="17" t="n">
         <v>-0.1125189107212077</v>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="17" t="n">
         <v>0.0231561831887904</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="17" t="n">
         <v>-0.0070658820926857</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="28" t="n">
         <v>-0.0805734197027545</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="28" t="n">
         <v>-0.0596758909696701</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="28" t="n">
         <v>0.1458106229539508</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="28" t="n">
         <v>-0.2599604463071995</v>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="27" t="n">
+      <c r="J14" s="28" t="n">
         <v>0.0209928798538189</v>
       </c>
-      <c r="K14" s="27" t="n">
+      <c r="K14" s="28" t="n">
         <v>0.0070464703305382</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="28" t="n">
         <v>-0.0723436224182088</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="28" t="n">
         <v>-0.218580848518051</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="28" t="n">
         <v>-0.07793667413424429</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="28" t="n">
         <v>-0.0069595372522321</v>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
+      <c r="J15" s="28" t="n">
         <v>0.0279986421832064</v>
       </c>
-      <c r="K15" s="27" t="n">
+      <c r="K15" s="28" t="n">
         <v>0.0063124281375852</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="28" t="n">
         <v>-0.1110708025535955</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="28" t="n">
         <v>0.1808376609273443</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="28" t="n">
         <v>0.3087414111063782</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="28" t="n">
         <v>-0.4371995375985574</v>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="27" t="n">
+      <c r="J16" s="28" t="n">
         <v>0.0254253869317556</v>
       </c>
-      <c r="K16" s="27" t="n">
+      <c r="K16" s="28" t="n">
         <v>0.0179805767303264</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="26" t="n">
         <v>-0.0743629892086322</v>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="26" t="n">
         <v>-0.1387634300955811</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <v>0.1041495071207343</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="H17" s="26" t="n">
         <v>-0.137952192271936</v>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
+      <c r="J17" s="26" t="n">
         <v>0.02615590712964</v>
       </c>
-      <c r="K17" s="25" t="n">
+      <c r="K17" s="26" t="n">
         <v>-0.0222670617351794</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="26" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="26" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n">
+      <c r="J18" s="26" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K18" s="25" t="n">
+      <c r="K18" s="26" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>-0.0858862988621121</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <v>-0.2407996860197412</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>-0.053257821777556</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="26" t="n">
         <v>-0.0414981713743457</v>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="J19" s="26" t="n">
         <v>0.0305942800876695</v>
       </c>
-      <c r="K19" s="25" t="n">
+      <c r="K19" s="26" t="n">
         <v>-0.0310153372448183</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <v>-0.0597432263673228</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="28" t="n">
         <v>-0.167161244124102</v>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="28" t="n">
         <v>-0.1621890850921175</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <v>-0.2601417240448666</v>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="27" t="n">
+      <c r="J20" s="28" t="n">
         <v>0.0215890519221315</v>
       </c>
-      <c r="K20" s="27" t="n">
+      <c r="K20" s="28" t="n">
         <v>0.0408327384185252</v>
       </c>
     </row>
@@ -3042,100 +3051,100 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Hisseler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>SISE.IS, BIMAS.IS, TOASO.IS, FROTO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Nakit kuralı</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Nitelikli fırsat sayısı</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3161,232 +3170,232 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
@@ -3412,94 +3421,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Gösterge</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -3531,342 +3540,342 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Aktif Pozisyon</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Giriş Tarihi</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Gerçekleşmemiş PnL</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Benchmark Getirisi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="29" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H4" s="29" t="n">
+      <c r="G4" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H4" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="29" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H5" s="29" t="n">
+      <c r="G5" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H5" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="29" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H6" s="29" t="n">
+      <c r="G6" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H6" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>104</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="29" t="n">
         <v>104</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H7" s="29" t="n">
+      <c r="G7" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H7" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H8" s="29" t="n">
+      <c r="G8" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H8" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="29" t="n">
         <v>45.5</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="29" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H9" s="29" t="n">
+      <c r="G9" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H9" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="29" t="n">
         <v>371.25</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="29" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="29" t="n">
         <v>-3.637978807091713e-12</v>
       </c>
-      <c r="G10" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H10" s="29" t="n">
+      <c r="G10" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H10" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>296</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="29" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H11" s="29" t="n">
+      <c r="G11" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H11" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="29" t="n">
         <v>384</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="29" t="n">
         <v>384</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H12" s="29" t="n">
+      <c r="G12" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H12" s="30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -41,9 +41,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
@@ -60,6 +57,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -105,19 +105,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -137,96 +131,93 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,595 +602,595 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BIST RankingBot Yatırımcı Raporu</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Piyasa Rejimi: Risk ON</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Aktif Model: volume_heavy</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı: 64.35/100</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>BU AY YAPILACAKLAR</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>AL: SISE.IS, FROTO.IS, BIMAS.IS, TOASO.IS, ARCLK.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>AZALT: ASELS.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ÇIK: EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NAKIT: %50</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Neden Nakit Tutuluyor?</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>- Yeterli sayıda yüksek kaliteli fırsat bulunamadı.</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>- Opportunity filter aktif.</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Tablo çekiciliğe göre sıralıdır; yüksek conviction daha güçlü adayları gösterir.</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Qualified opportunities count: 5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Allocation TL</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Expected Return %</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Expected Return TL</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Stop Price</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Risk/Reward</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Conviction</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Rejected opportunities count: 5</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.1243871586137416</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>12438.71586137416</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="7" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>713.1262528103351</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="8" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="8" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Cash allocation %: %50</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="7" t="n">
         <v>0.1065382972466226</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>10653.82972466226</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>1209.604218552528</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="8" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="8" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="7" t="n">
         <v>0.09833656824386003</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>9833.656824386002</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="7" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>147.5572851699831</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="8" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="8" t="n">
         <v>352.6875</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>0.3001066394834209</v>
       </c>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="7" t="n">
         <v>0.09391563882388926</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>9391.563882388926</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="7" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>337.7588530847005</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="8" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="8" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="6" t="n">
         <v>0.5672232190119821</v>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="7" t="n">
         <v>0.07682233707188654</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>7682.233707188654</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="7" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>244.7772522795647</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="8" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>0.6372554171334678</v>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="13" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1238,944 +1229,944 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Aylık Yatırımcı Özeti</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Toplam önerilen/satılacak satır: 13</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Renkler: AL yeşil, TUT sarı, SAT kırmızı.</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bu rapor araştırma amaçlıdır; otomatik emir veya yatırım tavsiyesi değildir.</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt %</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta %</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst %</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt Fiyat</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta Fiyat</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst Fiyat</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Stop / Risk Fiyatı</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Ana Sebep</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Risk Notu</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.0420559802578865</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1156036872656343</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="15" t="n">
         <v>38.31776078968454</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="15" t="n">
         <v>39.79358124262377</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="15" t="n">
         <v>44.62414749062538</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="15" t="n">
         <v>37.54126859386067</v>
       </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="15" t="n">
+      <c r="M8" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="15" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="18" t="n">
+      <c r="M9" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="19" t="n">
         <v>-0.0046916890080428</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.1020951406282874</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>369.5082104557641</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>409.1528209582517</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>352.6875</v>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="18" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.06340373236672001</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.07252410609256819</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>317.4671354034002</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="18" t="n">
+      <c r="M11" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>102.5999984741211</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="16" t="n">
         <v>-0.0448028308183779</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>0.0559687682788319</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="15" t="n">
         <v>98.00322810051922</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="15" t="n">
         <v>102.0206973756039</v>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="15" t="n">
         <v>108.3423940141277</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="15" t="n">
         <v>97.46999855041503</v>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="15" t="n">
+      <c r="M12" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N12" s="15" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="15" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>23.05999946594238</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0633746386509592</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.0814151454989152</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="15" t="n">
         <v>21.59858033249697</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="15" t="n">
         <v>22.38352252170423</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="15" t="n">
         <v>24.93743267766699</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="15" t="n">
         <v>21.56527333559732</v>
       </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="15" t="n">
+      <c r="M13" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="21" t="n">
         <v>384</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="22" t="n">
         <v>-0.0281690730134268</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="22" t="n">
         <v>0.08543155919911009</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="21" t="n">
         <v>373.1830759628441</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="21" t="n">
         <v>389.7266192813116</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="21" t="n">
         <v>416.8057187324583</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="21" t="n">
         <v>359.9101054961429</v>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="21" t="n">
+      <c r="M14" s="20" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="19" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="18" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <v>104</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="19" t="n">
         <v>-0.0155083176665838</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.08243455158337749</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="18" t="n">
         <v>102.3871349626753</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>112.5731933646713</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>98.8</v>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="18" t="n">
+      <c r="M16" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="N16" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O16" s="18" t="inlineStr">
+      <c r="O16" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="15" t="n">
         <v>291.5</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="16" t="n">
         <v>-0.0386983355086648</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="16" t="n">
         <v>0.0471518681568155</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="15" t="n">
         <v>280.2194351992242</v>
       </c>
-      <c r="I17" s="16" t="n">
+      <c r="I17" s="15" t="n">
         <v>289.4402953699822</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="15" t="n">
         <v>305.2447695677117</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="15" t="n">
         <v>276.925</v>
       </c>
-      <c r="L17" s="15" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="15" t="n">
+      <c r="M17" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N17" s="15" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O17" s="15" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="24" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.09996593281665379</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0287358367126191</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="24" t="n">
         <v>87.01823150556903</v>
       </c>
-      <c r="J18" s="25" t="n">
+      <c r="J18" s="24" t="n">
         <v>91.55748946742311</v>
       </c>
-      <c r="K18" s="25" t="n">
+      <c r="K18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n">
+      <c r="M18" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N18" s="24" t="inlineStr">
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif</t>
         </is>
       </c>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="24" t="n">
         <v>63.70000076293945</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0615218226622063</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>0.1090908628521543</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="24" t="n">
         <v>59.78106061241949</v>
       </c>
-      <c r="I19" s="25" t="n">
+      <c r="I19" s="24" t="n">
         <v>63.40140776872636</v>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="J19" s="24" t="n">
         <v>70.64908880985141</v>
       </c>
-      <c r="K19" s="25" t="n">
+      <c r="K19" s="24" t="n">
         <v>59.66295737853054</v>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n">
+      <c r="M19" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N19" s="24" t="inlineStr">
+      <c r="N19" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var</t>
         </is>
       </c>
-      <c r="O19" s="24" t="inlineStr">
+      <c r="O19" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="24" t="n">
         <v>33.41999816894531</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="25" t="n">
         <v>-0.0659425781939114</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="25" t="n">
         <v>0.1010665940075984</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="I20" s="25" t="n">
+      <c r="I20" s="24" t="n">
         <v>32.38346565501426</v>
       </c>
-      <c r="J20" s="25" t="n">
+      <c r="J20" s="24" t="n">
         <v>36.79764355562079</v>
       </c>
-      <c r="K20" s="25" t="n">
+      <c r="K20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n">
+      <c r="M20" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="N20" s="23" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O20" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
@@ -2210,824 +2201,824 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1A Momentum</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>3A Momentum</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>6A Momentum</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Hacim Değişimi</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Trend Durumu</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Beklenen Getiri Orta %</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="16" t="n">
         <v>0.1862395774600724</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="16" t="n">
         <v>0.2539185102925374</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="16" t="n">
         <v>0.6764458917342262</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="16" t="n">
         <v>0.041267190077997</v>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="16" t="n">
         <v>0.0307341425767416</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="J5" s="19" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="K5" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.0013486176668915</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.100815418828762</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.3632607485858201</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="19" t="n">
         <v>-0.1103780044876269</v>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="19" t="n">
         <v>0.023589744633299</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="19" t="n">
         <v>-0.0025273799494524</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>-0.0189264227791532</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.3768329115958089</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>-0.1760804208636897</v>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="19" t="n">
         <v>0.0273607577956114</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.08474576386540381</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.1506622857438071</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1173328587488999</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="16" t="n">
         <v>0.0313938948468988</v>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>0.0219305756012054</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="16" t="n">
         <v>-0.07091056609677771</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="16" t="n">
         <v>0.3013544220943314</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <v>0.35647055682014</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="16" t="n">
         <v>-0.4658997689756274</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="16" t="n">
         <v>0.0324095005412434</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>-0.0975323149236192</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="22" t="n">
         <v>0.234726688102894</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="22" t="n">
         <v>1.093784148197624</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="22" t="n">
         <v>-0.3248706883042701</v>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="22" t="n">
         <v>0.0313670501352306</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="19" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="19" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="19" t="n">
         <v>-0.0739091970276476</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <v>-0.1231028554971428</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>-0.0160832260863227</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="19" t="n">
         <v>-0.0886630889314125</v>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="19" t="n">
         <v>0.0203560631794317</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0731319554848967</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0642054574638844</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.068744271310724</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="16" t="n">
         <v>-0.1125189107212077</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="16" t="n">
         <v>0.0231561831887904</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="K13" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="27" t="n">
         <v>-0.0805734197027545</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="27" t="n">
         <v>-0.0596758909696701</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="27" t="n">
         <v>0.1458106229539508</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="27" t="n">
         <v>-0.2599604463071995</v>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="27" t="n">
         <v>0.0209928798538189</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="27" t="n">
         <v>0.0070464703305382</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="27" t="n">
         <v>-0.0723436224182088</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="27" t="n">
         <v>-0.218580848518051</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="27" t="n">
         <v>-0.07793667413424429</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="27" t="n">
         <v>-0.0069595372522321</v>
       </c>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="27" t="n">
         <v>0.0279986421832064</v>
       </c>
-      <c r="K15" s="28" t="n">
+      <c r="K15" s="27" t="n">
         <v>0.0063124281375852</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="27" t="n">
         <v>-0.1110708025535955</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="27" t="n">
         <v>0.1808376609273443</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="27" t="n">
         <v>0.3087414111063782</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="27" t="n">
         <v>-0.4371995375985574</v>
       </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="27" t="n">
         <v>0.0254253869317556</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="27" t="n">
         <v>0.0179805767303264</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="25" t="n">
         <v>-0.0743629892086322</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="25" t="n">
         <v>-0.1387634300955811</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="25" t="n">
         <v>0.1041495071207343</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="25" t="n">
         <v>-0.137952192271936</v>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="25" t="n">
         <v>0.02615590712964</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="25" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="25" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0858862988621121</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.2407996860197412</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>-0.053257821777556</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="25" t="n">
         <v>-0.0414981713743457</v>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="25" t="n">
         <v>0.0305942800876695</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="27" t="n">
         <v>-0.0597432263673228</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="27" t="n">
         <v>-0.167161244124102</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="27" t="n">
         <v>-0.1621890850921175</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="27" t="n">
         <v>-0.2601417240448666</v>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="28" t="n">
+      <c r="J20" s="27" t="n">
         <v>0.0215890519221315</v>
       </c>
-      <c r="K20" s="28" t="n">
+      <c r="K20" s="27" t="n">
         <v>0.0408327384185252</v>
       </c>
     </row>
@@ -3051,100 +3042,100 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisseler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>SISE.IS, BIMAS.IS, TOASO.IS, FROTO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Nakit kuralı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nitelikli fırsat sayısı</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3170,232 +3161,232 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
@@ -3421,94 +3412,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Gösterge</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -3540,342 +3531,342 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Aktif Pozisyon</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Giriş Tarihi</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Gerçekleşmemiş PnL</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Benchmark Getirisi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H4" s="30" t="n">
+      <c r="G4" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H4" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H5" s="30" t="n">
+      <c r="G5" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H5" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H6" s="30" t="n">
+      <c r="G6" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H6" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H7" s="30" t="n">
+      <c r="G7" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H7" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H8" s="30" t="n">
+      <c r="G8" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H8" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H9" s="30" t="n">
+      <c r="G9" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H9" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="28" t="n">
         <v>-3.637978807091713e-12</v>
       </c>
-      <c r="G10" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H10" s="30" t="n">
+      <c r="G10" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H11" s="30" t="n">
+      <c r="G11" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H11" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H12" s="30" t="n">
+      <c r="G12" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H12" s="29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report_2026-06-01.xlsx
+++ b/results/monthly_investor_report_2026-06-01.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>
